--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290133</v>
+        <v>125290142</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455153</v>
+        <v>454991</v>
       </c>
       <c r="R2" t="n">
-        <v>7046776</v>
+        <v>7046774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290142</v>
+        <v>125290133</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454991</v>
+        <v>455153</v>
       </c>
       <c r="R5" t="n">
-        <v>7046774</v>
+        <v>7046776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290142</v>
+        <v>125290139</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454991</v>
+        <v>455089</v>
       </c>
       <c r="R2" t="n">
-        <v>7046774</v>
+        <v>7046590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125290140</v>
+        <v>125290142</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455164</v>
+        <v>454991</v>
       </c>
       <c r="R3" t="n">
-        <v>7046776</v>
+        <v>7046774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125290139</v>
+        <v>125290133</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455089</v>
+        <v>455153</v>
       </c>
       <c r="R4" t="n">
-        <v>7046590</v>
+        <v>7046776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290133</v>
+        <v>125290140</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455153</v>
+        <v>455164</v>
       </c>
       <c r="R5" t="n">
         <v>7046776</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290139</v>
+        <v>125290133</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455089</v>
+        <v>455153</v>
       </c>
       <c r="R2" t="n">
-        <v>7046590</v>
+        <v>7046776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125290133</v>
+        <v>125290140</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455153</v>
+        <v>455164</v>
       </c>
       <c r="R4" t="n">
         <v>7046776</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290140</v>
+        <v>125290139</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455164</v>
+        <v>455089</v>
       </c>
       <c r="R5" t="n">
-        <v>7046776</v>
+        <v>7046590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125290140</v>
+        <v>125290139</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455164</v>
+        <v>455089</v>
       </c>
       <c r="R4" t="n">
-        <v>7046776</v>
+        <v>7046590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290139</v>
+        <v>125290140</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455089</v>
+        <v>455164</v>
       </c>
       <c r="R5" t="n">
-        <v>7046590</v>
+        <v>7046776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290133</v>
+        <v>125290140</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455153</v>
+        <v>455164</v>
       </c>
       <c r="R2" t="n">
         <v>7046776</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125290142</v>
+        <v>125290133</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454991</v>
+        <v>455153</v>
       </c>
       <c r="R3" t="n">
-        <v>7046774</v>
+        <v>7046776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290140</v>
+        <v>125290142</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455164</v>
+        <v>454991</v>
       </c>
       <c r="R5" t="n">
-        <v>7046776</v>
+        <v>7046774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290140</v>
+        <v>125290139</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455164</v>
+        <v>455089</v>
       </c>
       <c r="R2" t="n">
-        <v>7046776</v>
+        <v>7046590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>125290133</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125290139</v>
+        <v>125290140</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455089</v>
+        <v>455164</v>
       </c>
       <c r="R4" t="n">
-        <v>7046590</v>
+        <v>7046776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>125290142</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>88512</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125290139</v>
+        <v>125290140</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
+        <v>91184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455089</v>
+        <v>455164</v>
       </c>
       <c r="R2" t="n">
-        <v>7046590</v>
+        <v>7046776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125290133</v>
+        <v>125290142</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>88512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455153</v>
+        <v>454991</v>
       </c>
       <c r="R3" t="n">
-        <v>7046776</v>
+        <v>7046774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125290140</v>
+        <v>125290139</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455164</v>
+        <v>455089</v>
       </c>
       <c r="R4" t="n">
-        <v>7046776</v>
+        <v>7046590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290142</v>
+        <v>125290133</v>
       </c>
       <c r="B5" t="n">
-        <v>88512</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454991</v>
+        <v>455153</v>
       </c>
       <c r="R5" t="n">
-        <v>7046774</v>
+        <v>7046776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125290142</v>
       </c>
       <c r="B2" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125290133</v>
       </c>
       <c r="B3" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125290140</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13383-2025 artfynd.xlsx
+++ b/artfynd/A 13383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125290142</v>
       </c>
       <c r="B2" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125290133</v>
       </c>
       <c r="B3" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125290140</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125290139</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
